--- a/output/20260630_fix_owner_new_import/active_problem_2_zero_price_direct_full_41_cases_20260630.xlsx
+++ b/output/20260630_fix_owner_new_import/active_problem_2_zero_price_direct_full_41_cases_20260630.xlsx
@@ -860,7 +860,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
     </row>

--- a/output/20260630_fix_owner_new_import/active_problem_2_zero_price_direct_full_41_cases_20260630.xlsx
+++ b/output/20260630_fix_owner_new_import/active_problem_2_zero_price_direct_full_41_cases_20260630.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Импорт_абонементы" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Импорт_абонементы'!$A$1:$T$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Импорт_абонементы'!$A$1:$U$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,326 +435,332 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T42"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="37" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="17" customWidth="1" min="19" max="19"/>
-    <col width="35" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="35" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>contract_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>client_fio</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>contract_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>card</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>duration</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>duration_type</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>create_date</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>payment_date</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>activation_date</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>end_date</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>freeze</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>guests</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>visits_left</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>amount_of_payments</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>payment_left</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>type_of_payment</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>manager</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>00000138477</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>000000086</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>+7 (953) 5392509</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Абрамян Игорь Геннадьевич</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>УЛЬТРА 12 месяцев + подарок</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>115000226241</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="H2" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="n">
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
         <v>43101</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>45870</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="L2" s="3" t="n">
+        <v>45870</v>
+      </c>
+      <c r="M2" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="N2" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="N2" s="2" t="n"/>
       <c r="O2" s="2" t="n"/>
-      <c r="P2" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>00000138478</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>000021782</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>+7 (911) 4385658, +0</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Абрамян Надежда Александровна</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>УЛЬТРА 12 месяцев + подарок</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>000040096209</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="H3" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="n">
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
         <v>43101</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>45870</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="L3" s="3" t="n">
+        <v>45870</v>
+      </c>
+      <c r="M3" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="N3" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
-      <c r="P3" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>00000147603</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>000072891</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>+7 (999) 2367539</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Андреев Александр Сергеевич</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Абонемент УЛЬТРА 12 месяцев</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>4111111121983</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="H4" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>46085</v>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
       </c>
       <c r="J4" s="3" t="n">
         <v>46085</v>
@@ -763,822 +769,833 @@
         <v>46085</v>
       </c>
       <c r="L4" s="3" t="n">
+        <v>46085</v>
+      </c>
+      <c r="M4" s="3" t="n">
         <v>46449</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="N4" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="N4" s="2" t="n"/>
       <c r="O4" s="2" t="n"/>
-      <c r="P4" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P4" s="2" t="n"/>
       <c r="Q4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>00000132160</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>000065365</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>+7 (953) 5277922</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Асадов Фазил Мубариз Оглы</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА 12 месяцев</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>000010008454</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="H5" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>45710</v>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
       </c>
       <c r="J5" s="3" t="n">
         <v>45710</v>
       </c>
       <c r="K5" s="3" t="n">
+        <v>45710</v>
+      </c>
+      <c r="L5" s="3" t="n">
         <v>45711</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="M5" s="3" t="n">
         <v>46256</v>
       </c>
-      <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
       <c r="O5" s="2" t="n"/>
-      <c r="P5" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P5" s="2" t="n"/>
       <c r="Q5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>00000140456</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>000001070</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>+7 (964) 3186744</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Бабушкина Ксения Игоревна</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА 12 месяцев</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>115000238947</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="H6" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="n">
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="n">
         <v>43540</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>45916</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>45916</v>
       </c>
       <c r="L6" s="3" t="n">
+        <v>45916</v>
+      </c>
+      <c r="M6" s="3" t="n">
         <v>46280</v>
       </c>
-      <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
       <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P6" s="2" t="n"/>
       <c r="Q6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>00000138467</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>000001350</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>+7 (921) 7272505</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Бахилин Алексей Евгеньевич</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА 12 месяцев + 2 месяца заморозки в подарок</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>115000257795</t>
         </is>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="H7" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="n">
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="n">
         <v>43760</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>45870</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="L7" s="3" t="n">
+        <v>45870</v>
+      </c>
+      <c r="M7" s="3" t="n">
         <v>46245</v>
       </c>
-      <c r="M7" s="2" t="n">
+      <c r="N7" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="N7" s="2" t="n"/>
       <c r="O7" s="2" t="n"/>
-      <c r="P7" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P7" s="2" t="n"/>
       <c r="Q7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>00000133616</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>000025211</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>+7 (953) 5279902</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Беляева Елена Васильевна</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА+6 месяцев в подарок</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>115000204942</t>
         </is>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="H8" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="n">
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="n">
         <v>43101</v>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="K8" s="3" t="n">
         <v>45747</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="L8" s="3" t="n">
         <v>45753</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="M8" s="3" t="n">
         <v>46297</v>
       </c>
-      <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="n"/>
-      <c r="P8" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P8" s="2" t="n"/>
       <c r="Q8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>00000134174</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>000001635</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>+7 (911) 4119519</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Бершедов Артур Евгеньевич</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА+6 месяцев в подарок</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>115000177208</t>
         </is>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="H9" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="n">
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="n">
         <v>43101</v>
       </c>
-      <c r="J9" s="3" t="n">
+      <c r="K9" s="3" t="n">
         <v>45761</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="L9" s="3" t="n">
         <v>45763</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="M9" s="3" t="n">
         <v>46310</v>
       </c>
-      <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="2" t="n"/>
-      <c r="P9" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P9" s="2" t="n"/>
       <c r="Q9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>00000136010</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>000002393</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>+7 (911) 4271889, +7 (911) 6615054</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Быкова Надежда Валерьевна</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Абонемент Ультра 15 месяцев (подарок)</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>9111111121926</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="H10" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n">
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="n">
         <v>43101</v>
       </c>
-      <c r="J10" s="3" t="n">
+      <c r="K10" s="3" t="n">
         <v>45808</v>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="L10" s="3" t="n">
         <v>45827</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="M10" s="3" t="n">
         <v>46283</v>
       </c>
-      <c r="M10" s="2" t="n">
+      <c r="N10" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="N10" s="2" t="n"/>
       <c r="O10" s="2" t="n"/>
-      <c r="P10" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P10" s="2" t="n"/>
       <c r="Q10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>00000150337</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>000029489</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>+7 (921) 4576471</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Ганжина Людмила Николаевна</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА 15 месяцев (подарок)</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>9111111121100</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="H11" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="n">
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="n">
         <v>43101</v>
       </c>
-      <c r="J11" s="3" t="n">
+      <c r="K11" s="3" t="n">
         <v>46157</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="L11" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="M11" s="3" t="n">
         <v>46633</v>
       </c>
-      <c r="M11" s="2" t="n">
+      <c r="N11" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="N11" s="2" t="n"/>
       <c r="O11" s="2" t="n"/>
-      <c r="P11" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P11" s="2" t="n"/>
       <c r="Q11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>00000143160</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>000012075</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>+7 (911) 0506704</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Генералова Ирина Сергеевна</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА 12 месяцев</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>115000249189</t>
         </is>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="H12" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="n">
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="n">
         <v>45012</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>45979</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>45979</v>
       </c>
       <c r="L12" s="3" t="n">
+        <v>45979</v>
+      </c>
+      <c r="M12" s="3" t="n">
         <v>46343</v>
       </c>
-      <c r="M12" s="2" t="n"/>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="2" t="n"/>
-      <c r="P12" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P12" s="2" t="n"/>
       <c r="Q12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>00000150339</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>000073892</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>+7 (953) 5299682</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Горобцева Евгения Валерьевна</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА 15 месяцев (подарок)</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>115000282216</t>
         </is>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="H13" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>46157</v>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
       </c>
       <c r="J13" s="3" t="n">
         <v>46157</v>
       </c>
       <c r="K13" s="3" t="n">
+        <v>46157</v>
+      </c>
+      <c r="L13" s="3" t="n">
         <v>46187</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="M13" s="3" t="n">
         <v>46643</v>
       </c>
-      <c r="M13" s="2" t="n">
+      <c r="N13" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="N13" s="2" t="n"/>
       <c r="O13" s="2" t="n"/>
-      <c r="P13" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P13" s="2" t="n"/>
       <c r="Q13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>00000138259</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>000068453</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>+7 (981) 4069549</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Гришин Матвей Андреевич</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Абонемент УЛЬТРА 12 месяцев (акция 2 мес. в подарок)</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>8211111112595</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="H14" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="n">
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="n">
         <v>45773</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>45867</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>45867</v>
       </c>
       <c r="L14" s="3" t="n">
+        <v>45867</v>
+      </c>
+      <c r="M14" s="3" t="n">
         <v>46231</v>
       </c>
-      <c r="M14" s="2" t="n"/>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="2" t="n"/>
-      <c r="P14" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P14" s="2" t="n"/>
       <c r="Q14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>00000134175</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>000025707</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>+7 (953) 5263506</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Евсеева Дарина Олеговна</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА 12 месяцев (подарок)</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>115000200760</t>
         </is>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="H15" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>45761</v>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
       </c>
       <c r="J15" s="3" t="n">
         <v>45761</v>
@@ -1587,148 +1604,150 @@
         <v>45761</v>
       </c>
       <c r="L15" s="3" t="n">
+        <v>45761</v>
+      </c>
+      <c r="M15" s="3" t="n">
         <v>46215</v>
       </c>
-      <c r="M15" s="2" t="n"/>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="n"/>
-      <c r="P15" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P15" s="2" t="n"/>
       <c r="Q15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>00000124791</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>000005379</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>+7 (953) 5266053</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Емельянов Алексей Николаевич</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИ 24 месяцев</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>115000201408</t>
         </is>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="H16" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="n">
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="n">
         <v>43101</v>
       </c>
-      <c r="J16" s="3" t="n">
+      <c r="K16" s="3" t="n">
         <v>45492</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="L16" s="3" t="n">
         <v>45495</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="M16" s="3" t="n">
         <v>46224</v>
       </c>
-      <c r="M16" s="2" t="n">
+      <c r="N16" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="N16" s="2" t="n"/>
       <c r="O16" s="2" t="n"/>
-      <c r="P16" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P16" s="2" t="n"/>
       <c r="Q16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S16" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>00000139318</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>000069754</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>+7 (953) 5287037</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Ермакова Елена Александровна</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Абонемент УЛЬТРА 12 месяцев</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>115000230712</t>
         </is>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="H17" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>45892</v>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
       </c>
       <c r="J17" s="3" t="n">
         <v>45892</v>
@@ -1737,146 +1756,148 @@
         <v>45892</v>
       </c>
       <c r="L17" s="3" t="n">
+        <v>45892</v>
+      </c>
+      <c r="M17" s="3" t="n">
         <v>46316</v>
       </c>
-      <c r="M17" s="2" t="n"/>
       <c r="N17" s="2" t="n"/>
       <c r="O17" s="2" t="n"/>
-      <c r="P17" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P17" s="2" t="n"/>
       <c r="Q17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>00000148562</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>000063755</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>+7 (921) 5202663</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Журавлева Валерия Васильевна</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА 12 месяцев (подарок)</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>2200000005748</t>
         </is>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="H18" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="n">
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="n">
         <v>45426</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>46107</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>46107</v>
       </c>
       <c r="L18" s="3" t="n">
+        <v>46107</v>
+      </c>
+      <c r="M18" s="3" t="n">
         <v>46563</v>
       </c>
-      <c r="M18" s="2" t="n"/>
       <c r="N18" s="2" t="n"/>
       <c r="O18" s="2" t="n"/>
-      <c r="P18" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P18" s="2" t="n"/>
       <c r="Q18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>00000143165</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>000071196</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>+7 (981) 4054188</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Иванов Алексей Константинович</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА 12 месяцев</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>115000251731</t>
         </is>
       </c>
-      <c r="G19" s="2" t="n">
+      <c r="H19" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>45979</v>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
       </c>
       <c r="J19" s="3" t="n">
         <v>45979</v>
@@ -1885,72 +1906,73 @@
         <v>45979</v>
       </c>
       <c r="L19" s="3" t="n">
+        <v>45979</v>
+      </c>
+      <c r="M19" s="3" t="n">
         <v>46343</v>
       </c>
-      <c r="M19" s="2" t="n"/>
       <c r="N19" s="2" t="n"/>
       <c r="O19" s="2" t="n"/>
-      <c r="P19" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P19" s="2" t="n"/>
       <c r="Q19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>00000145855</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>000072211</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>+7 (911) 4131785</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Иванов Сергей Никитич</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Абонемент УЛЬТРА 12 месяцев СПЕЦПРЕДЛОЖЕНИЕ+подарок</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>000010004678</t>
         </is>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="H20" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>46046</v>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
       </c>
       <c r="J20" s="3" t="n">
         <v>46046</v>
@@ -1959,370 +1981,375 @@
         <v>46046</v>
       </c>
       <c r="L20" s="3" t="n">
+        <v>46046</v>
+      </c>
+      <c r="M20" s="3" t="n">
         <v>46500</v>
       </c>
-      <c r="M20" s="2" t="n"/>
       <c r="N20" s="2" t="n"/>
       <c r="O20" s="2" t="n"/>
-      <c r="P20" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P20" s="2" t="n"/>
       <c r="Q20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>00000133918</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>000056053</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>+7 (931) 7012976</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Ивановская Наталия Игоревна</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА+6 месяцев в подарок</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>1111111123836</t>
         </is>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="H21" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="n">
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="n">
         <v>44949</v>
       </c>
-      <c r="J21" s="3" t="n">
+      <c r="K21" s="3" t="n">
         <v>45754</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="L21" s="3" t="n">
         <v>45756</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="M21" s="3" t="n">
         <v>46303</v>
       </c>
-      <c r="M21" s="2" t="n"/>
       <c r="N21" s="2" t="n"/>
       <c r="O21" s="2" t="n"/>
-      <c r="P21" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P21" s="2" t="n"/>
       <c r="Q21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>00000133832</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>000043263</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>+7 (911) 4000305</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Ифтодий Андрей Семенович</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА+6 месяцев в подарок</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>9111111116830</t>
         </is>
       </c>
-      <c r="G22" s="2" t="n">
+      <c r="H22" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="n">
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="n">
         <v>44216</v>
       </c>
-      <c r="J22" s="3" t="n">
+      <c r="K22" s="3" t="n">
         <v>45752</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="L22" s="3" t="n">
         <v>45797</v>
       </c>
-      <c r="L22" s="3" t="n">
+      <c r="M22" s="3" t="n">
         <v>46344</v>
       </c>
-      <c r="M22" s="2" t="n"/>
       <c r="N22" s="2" t="n"/>
       <c r="O22" s="2" t="n"/>
-      <c r="P22" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P22" s="2" t="n"/>
       <c r="Q22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>00000134177</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>000024511</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>+7 (981) 4047626</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Ифтодий Виктория Андреевна</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА+6 месяцев в подарок</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>115000151499</t>
         </is>
       </c>
-      <c r="G23" s="2" t="n">
+      <c r="H23" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="n">
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="n">
         <v>43101</v>
       </c>
-      <c r="J23" s="3" t="n">
+      <c r="K23" s="3" t="n">
         <v>45761</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="L23" s="3" t="n">
         <v>45770</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="M23" s="3" t="n">
         <v>46317</v>
       </c>
-      <c r="M23" s="2" t="n"/>
       <c r="N23" s="2" t="n"/>
       <c r="O23" s="2" t="n"/>
-      <c r="P23" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P23" s="2" t="n"/>
       <c r="Q23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
         <is>
           <t>сбп</t>
         </is>
       </c>
-      <c r="T23" s="2" t="inlineStr">
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>00000145964</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>000060342</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>+7 (911) 0531326</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Калабанова Алена Витальевна</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Абонемент УЛЬТРА 12 месяцев СПЕЦПРЕДЛОЖЕНИЕ+подарок</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>000010004999</t>
         </is>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="H24" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="n">
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="n">
         <v>45356</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>46048</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>46048</v>
       </c>
       <c r="L24" s="3" t="n">
+        <v>46048</v>
+      </c>
+      <c r="M24" s="3" t="n">
         <v>46449</v>
       </c>
-      <c r="M24" s="2" t="n">
+      <c r="N24" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="N24" s="2" t="n"/>
       <c r="O24" s="2" t="n"/>
-      <c r="P24" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P24" s="2" t="n"/>
       <c r="Q24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>00000143325</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>000071255</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>+7 (900) 4639937</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Капусткин Никита Алексеевич</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА 12 месяцев</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>115000251007</t>
         </is>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="H25" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>45983</v>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
       </c>
       <c r="J25" s="3" t="n">
         <v>45983</v>
@@ -2331,222 +2358,225 @@
         <v>45983</v>
       </c>
       <c r="L25" s="3" t="n">
+        <v>45983</v>
+      </c>
+      <c r="M25" s="3" t="n">
         <v>46347</v>
       </c>
-      <c r="M25" s="2" t="n"/>
       <c r="N25" s="2" t="n"/>
       <c r="O25" s="2" t="n"/>
-      <c r="P25" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P25" s="2" t="n"/>
       <c r="Q25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>00000135731</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>000060656</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>+7 (953) 5338125</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Карнюшин Павел Сергеевич</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Абонемент Ультра 15 месяцев (подарок)</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>115000214323</t>
         </is>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="H26" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="n">
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="n">
         <v>45219</v>
       </c>
-      <c r="J26" s="3" t="n">
+      <c r="K26" s="3" t="n">
         <v>45806</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="L26" s="3" t="n">
         <v>45986</v>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="M26" s="3" t="n">
         <v>46442</v>
       </c>
-      <c r="M26" s="2" t="n">
+      <c r="N26" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="N26" s="2" t="n"/>
       <c r="O26" s="2" t="n"/>
-      <c r="P26" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P26" s="2" t="n"/>
       <c r="Q26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>00000147636</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>000018950</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>+7 (911) 4308773</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Козлова Мария Владимировна</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>УЛЬТРА 12 месяцев + подарок</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>115000269507</t>
         </is>
       </c>
-      <c r="G27" s="2" t="n">
+      <c r="H27" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="n">
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="n">
         <v>44895</v>
       </c>
-      <c r="J27" s="3" t="n">
+      <c r="K27" s="3" t="n">
         <v>46085</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="L27" s="3" t="n">
         <v>46140</v>
       </c>
-      <c r="L27" s="3" t="n">
+      <c r="M27" s="3" t="n">
         <v>46594</v>
       </c>
-      <c r="M27" s="2" t="n"/>
       <c r="N27" s="2" t="n"/>
       <c r="O27" s="2" t="n"/>
-      <c r="P27" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P27" s="2" t="n"/>
       <c r="Q27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>00000136195</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>000068885</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>+7 (996) 1121337</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Кулешов Николай Евгеньевич</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Абонемент УЛЬТРА 12 месяцев (акция 3 мес. в подарок)</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>000010007204</t>
         </is>
       </c>
-      <c r="G28" s="2" t="n">
+      <c r="H28" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="n">
-        <v>45814</v>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
       </c>
       <c r="J28" s="3" t="n">
         <v>45814</v>
@@ -2555,72 +2585,73 @@
         <v>45814</v>
       </c>
       <c r="L28" s="3" t="n">
+        <v>45814</v>
+      </c>
+      <c r="M28" s="3" t="n">
         <v>46271</v>
       </c>
-      <c r="M28" s="2" t="n"/>
       <c r="N28" s="2" t="n"/>
       <c r="O28" s="2" t="n"/>
-      <c r="P28" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P28" s="2" t="n"/>
       <c r="Q28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S28" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>00000144980</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>000071805</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>+7 (953) 5326081</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Ластовский Богдан Владимирович</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА 15 месяцев</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>115000261358</t>
         </is>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="H29" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="n">
-        <v>46024</v>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
       </c>
       <c r="J29" s="3" t="n">
         <v>46024</v>
@@ -2629,296 +2660,300 @@
         <v>46024</v>
       </c>
       <c r="L29" s="3" t="n">
+        <v>46024</v>
+      </c>
+      <c r="M29" s="3" t="n">
         <v>46478</v>
       </c>
-      <c r="M29" s="2" t="n"/>
       <c r="N29" s="2" t="n"/>
       <c r="O29" s="2" t="n"/>
-      <c r="P29" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P29" s="2" t="n"/>
       <c r="Q29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>00000134183</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>000063203</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>+7 (981) 4025325</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Ложкина Наталья Васильевна</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА+6 месяцев в подарок</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>115000200777</t>
         </is>
       </c>
-      <c r="G30" s="2" t="n">
+      <c r="H30" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="n">
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="n">
         <v>45427</v>
       </c>
-      <c r="J30" s="3" t="n">
+      <c r="K30" s="3" t="n">
         <v>45761</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="L30" s="3" t="n">
         <v>45792</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="M30" s="3" t="n">
         <v>46339</v>
       </c>
-      <c r="M30" s="2" t="n"/>
       <c r="N30" s="2" t="n"/>
       <c r="O30" s="2" t="n"/>
-      <c r="P30" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P30" s="2" t="n"/>
       <c r="Q30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S30" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>00000140594</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>000056530</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>+7 (953) 5262862</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Нескоромный Егор Олегович</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Абонемент УЛЬТРА 12 месяцев</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>115000170742</t>
         </is>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="H31" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="n">
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="n">
         <v>44970</v>
-      </c>
-      <c r="J31" s="3" t="n">
-        <v>45920</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>45920</v>
       </c>
       <c r="L31" s="3" t="n">
+        <v>45920</v>
+      </c>
+      <c r="M31" s="3" t="n">
         <v>46284</v>
       </c>
-      <c r="M31" s="2" t="n"/>
       <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="n"/>
-      <c r="P31" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P31" s="2" t="n"/>
       <c r="Q31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>00000135375</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>000012715</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>+7 (911) 4322544</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Новожилов Никита Сергеевич</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Абонемент Ультра 15 месяцев (подарок)</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>115000209169</t>
         </is>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="H32" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="n">
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="n">
         <v>43608</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>45798</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>45798</v>
       </c>
       <c r="L32" s="3" t="n">
+        <v>45798</v>
+      </c>
+      <c r="M32" s="3" t="n">
         <v>46326</v>
       </c>
-      <c r="M32" s="2" t="n">
+      <c r="N32" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="N32" s="2" t="n"/>
       <c r="O32" s="2" t="n"/>
-      <c r="P32" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P32" s="2" t="n"/>
       <c r="Q32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S32" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>00000148373</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>000073172</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>+7 (905) 2580016</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Отаджанов Мансурбек Кодирберди Угли</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Абонемент УЛЬТРА 12 месяцев СПЕЦПРЕДЛОЖЕНИЕ</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>8821111120737</t>
         </is>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="H33" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>46102</v>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
       </c>
       <c r="J33" s="3" t="n">
         <v>46102</v>
@@ -2927,72 +2962,73 @@
         <v>46102</v>
       </c>
       <c r="L33" s="3" t="n">
+        <v>46102</v>
+      </c>
+      <c r="M33" s="3" t="n">
         <v>46558</v>
       </c>
-      <c r="M33" s="2" t="n"/>
       <c r="N33" s="2" t="n"/>
       <c r="O33" s="2" t="n"/>
-      <c r="P33" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P33" s="2" t="n"/>
       <c r="Q33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>00000143128</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>000071182</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>+7 (921) 4651704</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Романов Сергей Константинович</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА 12 месяцев</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>115000249363</t>
         </is>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="H34" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v>45978</v>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
       </c>
       <c r="J34" s="3" t="n">
         <v>45978</v>
@@ -3001,222 +3037,225 @@
         <v>45978</v>
       </c>
       <c r="L34" s="3" t="n">
+        <v>45978</v>
+      </c>
+      <c r="M34" s="3" t="n">
         <v>46342</v>
       </c>
-      <c r="M34" s="2" t="n"/>
       <c r="N34" s="2" t="n"/>
       <c r="O34" s="2" t="n"/>
-      <c r="P34" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P34" s="2" t="n"/>
       <c r="Q34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>00000150527</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>000046782</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>+7 (921) 4563493</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Тикки Анна Владимировна</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА 15 месяцев (подарок)</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>115000273276</t>
         </is>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="H35" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="n">
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="n">
         <v>44374</v>
-      </c>
-      <c r="J35" s="3" t="n">
-        <v>46164</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>46164</v>
       </c>
       <c r="L35" s="3" t="n">
+        <v>46164</v>
+      </c>
+      <c r="M35" s="3" t="n">
         <v>46620</v>
       </c>
-      <c r="M35" s="2" t="n">
+      <c r="N35" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="N35" s="2" t="n"/>
       <c r="O35" s="2" t="n"/>
-      <c r="P35" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P35" s="2" t="n"/>
       <c r="Q35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>00000148508</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>000028941</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>+7 (911) 4109903</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Тимофеева Алина Раймовна</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Абонемент УЛЬТРА 12 месяцев СПЕЦПРЕДЛОЖЕНИЕ</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>4111111122447</t>
         </is>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="H36" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="n">
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="n">
         <v>43101</v>
       </c>
-      <c r="J36" s="3" t="n">
+      <c r="K36" s="3" t="n">
         <v>46106</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="L36" s="3" t="n">
         <v>46152</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="M36" s="3" t="n">
         <v>46608</v>
       </c>
-      <c r="M36" s="2" t="n"/>
       <c r="N36" s="2" t="n"/>
       <c r="O36" s="2" t="n"/>
-      <c r="P36" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P36" s="2" t="n"/>
       <c r="Q36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>00000142255</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>000070899</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>796010195123</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Титов Даниил Иванович</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА 12 месяцев</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>115000267824</t>
         </is>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="H37" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="n">
-        <v>45963</v>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
       </c>
       <c r="J37" s="3" t="n">
         <v>45963</v>
@@ -3225,222 +3264,225 @@
         <v>45963</v>
       </c>
       <c r="L37" s="3" t="n">
+        <v>45963</v>
+      </c>
+      <c r="M37" s="3" t="n">
         <v>46327</v>
       </c>
-      <c r="M37" s="2" t="n"/>
       <c r="N37" s="2" t="n"/>
       <c r="O37" s="2" t="n"/>
-      <c r="P37" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P37" s="2" t="n"/>
       <c r="Q37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>00000150429</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>000034959</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>+7 (902) 7703911</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Ткачук Алина Витальевна</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА 15 месяцев (подарок) спецпредложение</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>115000271838</t>
         </is>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="H38" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="n">
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="n">
         <v>45744</v>
       </c>
-      <c r="J38" s="3" t="n">
+      <c r="K38" s="3" t="n">
         <v>46161</v>
       </c>
-      <c r="K38" s="3" t="n">
+      <c r="L38" s="3" t="n">
         <v>46170</v>
       </c>
-      <c r="L38" s="3" t="n">
+      <c r="M38" s="3" t="n">
         <v>46626</v>
       </c>
-      <c r="M38" s="2" t="n">
+      <c r="N38" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="N38" s="2" t="n"/>
       <c r="O38" s="2" t="n"/>
-      <c r="P38" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P38" s="2" t="n"/>
       <c r="Q38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R38" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S38" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="2" t="n"/>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>00000133446</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>000018237</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>+7 (921) 2266167</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Туркова Ольга Геннадьевна</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА+6 месяцев в подарок</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>115000235502</t>
         </is>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="H39" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="n">
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="n">
         <v>43101</v>
       </c>
-      <c r="J39" s="3" t="n">
+      <c r="K39" s="3" t="n">
         <v>45743</v>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="L39" s="3" t="n">
         <v>45979</v>
       </c>
-      <c r="L39" s="3" t="n">
+      <c r="M39" s="3" t="n">
         <v>46523</v>
       </c>
-      <c r="M39" s="2" t="n"/>
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="n"/>
-      <c r="P39" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P39" s="2" t="n"/>
       <c r="Q39" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="2" t="n"/>
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>00000134111</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>000027270</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>+7 (909) 5722644</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Федосеева Ольга Сергеевна</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА+6 месяцев в подарок</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>9111111111811</t>
         </is>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="H40" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>45759</v>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
       </c>
       <c r="J40" s="3" t="n">
         <v>45759</v>
@@ -3449,183 +3491,188 @@
         <v>45759</v>
       </c>
       <c r="L40" s="3" t="n">
+        <v>45759</v>
+      </c>
+      <c r="M40" s="3" t="n">
         <v>46309</v>
       </c>
-      <c r="M40" s="2" t="n"/>
       <c r="N40" s="2" t="n"/>
       <c r="O40" s="2" t="n"/>
-      <c r="P40" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P40" s="2" t="n"/>
       <c r="Q40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S40" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>00000140230</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>000064760</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>+7 (911) 4242789, +7 (911) 4242783</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Фомина Людмила Александровна</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Абонемент УЛЬТРА 12 месяцев + 3 месяца заморозки в подарок</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>115000236974</t>
         </is>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="H41" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="n">
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="n">
         <v>45481</v>
       </c>
-      <c r="J41" s="3" t="n">
+      <c r="K41" s="3" t="n">
         <v>45911</v>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="L41" s="3" t="n">
         <v>45941</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="M41" s="3" t="n">
         <v>46395</v>
       </c>
-      <c r="M41" s="2" t="n"/>
       <c r="N41" s="2" t="n"/>
       <c r="O41" s="2" t="n"/>
-      <c r="P41" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P41" s="2" t="n"/>
       <c r="Q41" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S41" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>00000134888</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>000063886</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>+7 (911) 4201146</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Шейнова Антонина Иванова</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Абонемент Ультра 15 месяцев (подарок)</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>115000206809</t>
         </is>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="H42" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>месяц</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="n">
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>месяц</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="n">
         <v>45430</v>
       </c>
-      <c r="J42" s="3" t="n">
+      <c r="K42" s="3" t="n">
         <v>45781</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="L42" s="3" t="n">
         <v>45811</v>
       </c>
-      <c r="L42" s="3" t="n">
+      <c r="M42" s="3" t="n">
         <v>46267</v>
       </c>
-      <c r="M42" s="2" t="n">
+      <c r="N42" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="N42" s="2" t="n"/>
       <c r="O42" s="2" t="n"/>
-      <c r="P42" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="P42" s="2" t="n"/>
       <c r="Q42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>безналичные</t>
-        </is>
+      <c r="S42" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
+          <t>безналичные</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T42"/>
+  <autoFilter ref="A1:U42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/20260630_fix_owner_new_import/active_problem_2_zero_price_direct_full_41_cases_20260630.xlsx
+++ b/output/20260630_fix_owner_new_import/active_problem_2_zero_price_direct_full_41_cases_20260630.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Импорт_абонементы" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Импорт_абонементы'!$A$1:$U$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Импорт_абонементы'!$A$1:$V$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U42"/>
+  <dimension ref="A1:V42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -459,6 +459,7 @@
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="17" customWidth="1" min="20" max="20"/>
     <col width="35" customWidth="1" min="21" max="21"/>
+    <col width="31" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -567,6 +568,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>филиал</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -644,6 +650,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -721,6 +732,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
@@ -796,6 +812,11 @@
       <c r="U4" s="2" t="inlineStr">
         <is>
           <t>Пеуна Анастасия Ивановна</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
         </is>
       </c>
     </row>
@@ -873,6 +894,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -948,6 +974,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
@@ -1023,6 +1054,11 @@
       <c r="U7" s="2" t="inlineStr">
         <is>
           <t>Васьковская Виктория Петровна</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
         </is>
       </c>
     </row>
@@ -1100,6 +1136,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -1175,6 +1216,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -1252,6 +1298,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -1327,6 +1378,11 @@
       <c r="U11" s="2" t="inlineStr">
         <is>
           <t>Мартынова Дарья Дмитриевна</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
         </is>
       </c>
     </row>
@@ -1404,6 +1460,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
@@ -1479,6 +1540,11 @@
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>Васильева Яна Денисовна</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
         </is>
       </c>
     </row>
@@ -1556,6 +1622,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
@@ -1631,6 +1702,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -1706,6 +1782,11 @@
       <c r="U16" s="2" t="inlineStr">
         <is>
           <t>Васьковская Виктория Петровна</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
         </is>
       </c>
     </row>
@@ -1783,6 +1864,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -1858,6 +1944,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
@@ -1933,6 +2024,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -2008,6 +2104,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
@@ -2083,6 +2184,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -2158,6 +2264,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
@@ -2233,6 +2344,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -2308,6 +2424,11 @@
       <c r="U24" s="2" t="inlineStr">
         <is>
           <t>Петрова Полина Владимировна</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
         </is>
       </c>
     </row>
@@ -2385,6 +2506,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -2460,6 +2586,11 @@
       <c r="U26" s="2" t="inlineStr">
         <is>
           <t>Седунова Анна Сергеевна</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
         </is>
       </c>
     </row>
@@ -2537,6 +2668,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -2612,6 +2748,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -2687,6 +2828,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -2762,6 +2908,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
@@ -2837,6 +2988,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
@@ -2912,6 +3068,11 @@
       <c r="U32" s="2" t="inlineStr">
         <is>
           <t>Фёдорова Надежда Сергеевна</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
         </is>
       </c>
     </row>
@@ -2989,6 +3150,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
@@ -3064,6 +3230,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
@@ -3139,6 +3310,11 @@
       <c r="U35" s="2" t="inlineStr">
         <is>
           <t>Абраамян Татьяна Викторовна</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
         </is>
       </c>
     </row>
@@ -3216,6 +3392,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
@@ -3291,6 +3472,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
@@ -3366,6 +3552,11 @@
       <c r="U38" s="2" t="inlineStr">
         <is>
           <t>Васильева Яна Денисовна</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
         </is>
       </c>
     </row>
@@ -3443,6 +3634,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
@@ -3518,6 +3714,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
@@ -3593,6 +3794,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
@@ -3670,9 +3876,14 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U42"/>
+  <autoFilter ref="A1:V42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>